--- a/tpl_soporte.xlsx
+++ b/tpl_soporte.xlsx
@@ -3808,302 +3808,674 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s"/>
-      <c r="G1" s="2" t="s"/>
-      <c r="H1" s="2" t="s"/>
-      <c r="I1" s="2" t="s"/>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s"/>
-      <c r="L1" s="2" t="s"/>
+      <c r="K1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s"/>
-      <c r="O1" s="2" t="s"/>
-      <c r="P1" s="2" t="s"/>
-      <c r="Q1" s="2" t="s"/>
+      <c r="N1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="R1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="2" t="s"/>
-      <c r="T1" s="2" t="s"/>
+      <c r="S1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="U1" s="2"/>
-      <c r="V1" s="2" t="s"/>
-      <c r="W1" s="2" t="s"/>
-      <c r="X1" s="2" t="s"/>
-      <c r="Y1" s="2" t="s"/>
+      <c r="V1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="Z1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="2" t="s"/>
-      <c r="AB1" s="2" t="s"/>
+      <c r="AA1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AC1" s="2"/>
-      <c r="AD1" s="2" t="s"/>
-      <c r="AE1" s="2" t="s"/>
-      <c r="AF1" s="2" t="s"/>
-      <c r="AG1" s="2" t="s"/>
+      <c r="AD1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="AH1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="2" t="s"/>
-      <c r="AJ1" s="2" t="s"/>
+      <c r="AI1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AK1" s="2"/>
-      <c r="AL1" s="2" t="s"/>
-      <c r="AM1" s="2" t="s"/>
-      <c r="AN1" s="2" t="s"/>
-      <c r="AO1" s="2" t="s"/>
+      <c r="AL1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="AP1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AQ1" s="2" t="s"/>
-      <c r="AR1" s="2" t="s"/>
+      <c r="AQ1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s"/>
-      <c r="AU1" s="2" t="s"/>
-      <c r="AV1" s="2" t="s"/>
-      <c r="AW1" s="2" t="s"/>
+      <c r="AT1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="AX1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AY1" s="2" t="s"/>
-      <c r="AZ1" s="2" t="s"/>
+      <c r="AY1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="BA1" s="2"/>
-      <c r="BB1" s="2" t="s"/>
-      <c r="BC1" s="2" t="s"/>
-      <c r="BD1" s="2" t="s"/>
-      <c r="BE1" s="2" t="s"/>
+      <c r="BB1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="BF1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="BG1" s="2" t="s"/>
-      <c r="BH1" s="2" t="s"/>
+      <c r="BG1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="BI1" s="2"/>
-      <c r="BJ1" s="2" t="s"/>
-      <c r="BK1" s="2" t="s"/>
-      <c r="BL1" s="2" t="s"/>
-      <c r="BM1" s="2" t="s"/>
+      <c r="BJ1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="BN1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="BO1" s="2" t="s"/>
-      <c r="BP1" s="2" t="s"/>
+      <c r="BO1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="BQ1" s="2"/>
-      <c r="BR1" s="2" t="s"/>
-      <c r="BS1" s="2" t="s"/>
-      <c r="BT1" s="2" t="s"/>
-      <c r="BU1" s="2" t="s"/>
+      <c r="BR1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="BV1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="BW1" s="2" t="s"/>
-      <c r="BX1" s="2" t="s"/>
+      <c r="BW1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BX1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="BY1" s="2"/>
-      <c r="BZ1" s="2" t="s"/>
-      <c r="CA1" s="2" t="s"/>
-      <c r="CB1" s="2" t="s"/>
-      <c r="CC1" s="2" t="s"/>
+      <c r="BZ1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="CA1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="CB1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CC1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="CD1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="CE1" s="2" t="s"/>
-      <c r="CF1" s="2" t="s"/>
+      <c r="CE1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="CG1" s="2"/>
-      <c r="CH1" s="2" t="s"/>
-      <c r="CI1" s="2" t="s"/>
-      <c r="CJ1" s="2" t="s"/>
-      <c r="CK1" s="2" t="s"/>
+      <c r="CH1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="CI1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="CJ1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CK1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="CL1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="CM1" s="2" t="s"/>
-      <c r="CN1" s="2" t="s"/>
+      <c r="CM1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="CO1" s="2"/>
-      <c r="CP1" s="2" t="s"/>
-      <c r="CQ1" s="2" t="s"/>
-      <c r="CR1" s="2" t="s"/>
-      <c r="CS1" s="2" t="s"/>
+      <c r="CP1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="CQ1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="CR1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CS1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="CT1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="CU1" s="2" t="s"/>
-      <c r="CV1" s="2" t="s"/>
+      <c r="CU1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="CV1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="CW1" s="2"/>
-      <c r="CX1" s="2" t="s"/>
-      <c r="CY1" s="2" t="s"/>
-      <c r="CZ1" s="2" t="s"/>
-      <c r="DA1" s="2" t="s"/>
+      <c r="CX1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="CY1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="CZ1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DA1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="DB1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="DC1" s="2" t="s"/>
-      <c r="DD1" s="2" t="s"/>
+      <c r="DC1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="DD1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="DE1" s="2"/>
-      <c r="DF1" s="2" t="s"/>
-      <c r="DG1" s="2" t="s"/>
-      <c r="DH1" s="2" t="s"/>
-      <c r="DI1" s="2" t="s"/>
+      <c r="DF1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="DG1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="DH1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DI1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="DJ1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="DK1" s="2" t="s"/>
-      <c r="DL1" s="2" t="s"/>
+      <c r="DK1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="DL1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="DM1" s="2"/>
-      <c r="DN1" s="2" t="s"/>
-      <c r="DO1" s="2" t="s"/>
-      <c r="DP1" s="2" t="s"/>
-      <c r="DQ1" s="2" t="s"/>
+      <c r="DN1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="DO1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="DP1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DQ1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="DR1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="DS1" s="2" t="s"/>
-      <c r="DT1" s="2" t="s"/>
+      <c r="DS1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="DT1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="DU1" s="2"/>
-      <c r="DV1" s="2" t="s"/>
-      <c r="DW1" s="2" t="s"/>
-      <c r="DX1" s="2" t="s"/>
-      <c r="DY1" s="2" t="s"/>
+      <c r="DV1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="DW1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="DX1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DY1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="DZ1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="EA1" s="2" t="s"/>
-      <c r="EB1" s="2" t="s"/>
+      <c r="EA1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="EB1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="EC1" s="2"/>
-      <c r="ED1" s="2" t="s"/>
-      <c r="EE1" s="2" t="s"/>
-      <c r="EF1" s="2" t="s"/>
-      <c r="EG1" s="2" t="s"/>
+      <c r="ED1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="EE1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="EF1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="EG1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="EH1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="EI1" s="2" t="s"/>
-      <c r="EJ1" s="2" t="s"/>
+      <c r="EI1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="EJ1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="EK1" s="2"/>
-      <c r="EL1" s="2" t="s"/>
-      <c r="EM1" s="2" t="s"/>
-      <c r="EN1" s="2" t="s"/>
-      <c r="EO1" s="2" t="s"/>
+      <c r="EL1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="EM1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="EN1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="EO1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="EP1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="EQ1" s="2" t="s"/>
-      <c r="ER1" s="2" t="s"/>
-      <c r="ET1" s="2" t="s"/>
-      <c r="EU1" s="2" t="s"/>
-      <c r="EV1" s="2" t="s"/>
-      <c r="EW1" s="2" t="s"/>
+      <c r="EQ1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="ER1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="ET1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="EU1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="EV1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="EW1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="EX1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="EY1" s="2" t="s"/>
-      <c r="EZ1" s="2" t="s"/>
-      <c r="FB1" s="2" t="s"/>
-      <c r="FC1" s="2" t="s"/>
-      <c r="FD1" s="2" t="s"/>
-      <c r="FE1" s="2" t="s"/>
+      <c r="EY1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="EZ1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="FB1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="FC1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="FD1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="FE1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="FF1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="FG1" s="2" t="s"/>
-      <c r="FH1" s="2" t="s"/>
-      <c r="FJ1" s="2" t="s"/>
-      <c r="FK1" s="2" t="s"/>
-      <c r="FL1" s="2" t="s"/>
-      <c r="FM1" s="2" t="s"/>
+      <c r="FG1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="FH1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="FJ1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="FK1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="FL1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="FM1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="FN1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="FO1" s="2" t="s"/>
-      <c r="FP1" s="2" t="s"/>
-      <c r="FR1" s="2" t="s"/>
-      <c r="FS1" s="2" t="s"/>
-      <c r="FT1" s="2" t="s"/>
-      <c r="FU1" s="2" t="s"/>
+      <c r="FO1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="FP1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="FR1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="FS1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="FT1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="FU1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="FV1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="FW1" s="2" t="s"/>
-      <c r="FX1" s="2" t="s"/>
-      <c r="FZ1" s="2" t="s"/>
-      <c r="GA1" s="2" t="s"/>
-      <c r="GB1" s="2" t="s"/>
-      <c r="GC1" s="2" t="s"/>
+      <c r="FW1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="FX1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="FZ1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="GA1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="GB1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="GC1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="GD1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="GE1" s="2" t="s"/>
-      <c r="GF1" s="2" t="s"/>
-      <c r="GH1" s="2" t="s"/>
-      <c r="GI1" s="2" t="s"/>
-      <c r="GJ1" s="2" t="s"/>
-      <c r="GK1" s="2" t="s"/>
+      <c r="GE1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="GF1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="GH1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="GI1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="GJ1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="GK1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="GL1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="GM1" s="2" t="s"/>
-      <c r="GN1" s="2" t="s"/>
-      <c r="GP1" s="2" t="s"/>
-      <c r="GQ1" s="2" t="s"/>
-      <c r="GR1" s="2" t="s"/>
-      <c r="GS1" s="2" t="s"/>
+      <c r="GM1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="GN1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="GP1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="GQ1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="GR1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="GS1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="GT1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="GU1" s="2" t="s"/>
-      <c r="GV1" s="2" t="s"/>
-      <c r="GX1" s="2" t="s"/>
-      <c r="GY1" s="2" t="s"/>
-      <c r="GZ1" s="2" t="s"/>
-      <c r="HA1" s="2" t="s"/>
+      <c r="GU1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="GV1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="GX1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="GY1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="GZ1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="HA1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="HB1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="HC1" s="2" t="s"/>
-      <c r="HD1" s="2" t="s"/>
-      <c r="HF1" s="2" t="s"/>
-      <c r="HG1" s="2" t="s"/>
-      <c r="HH1" s="2" t="s"/>
-      <c r="HI1" s="2" t="s"/>
+      <c r="HC1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="HD1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="HF1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="HG1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="HH1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="HI1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="HJ1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="HK1" s="2" t="s"/>
-      <c r="HL1" s="2" t="s"/>
-      <c r="HN1" s="2" t="s"/>
-      <c r="HO1" s="2" t="s"/>
-      <c r="HP1" s="2" t="s"/>
-      <c r="HQ1" s="2" t="s"/>
+      <c r="HK1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="HL1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="HN1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="HO1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="HP1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="HQ1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="HR1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="HS1" s="2" t="s"/>
-      <c r="HT1" s="2" t="s"/>
-      <c r="HV1" s="2" t="s"/>
-      <c r="HW1" s="2" t="s"/>
-      <c r="HX1" s="2" t="s"/>
-      <c r="HY1" s="2" t="s"/>
+      <c r="HS1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="HT1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="HV1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="HW1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="HX1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="HY1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="HZ1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="IA1" s="2" t="s"/>
-      <c r="IB1" s="2" t="s"/>
-      <c r="ID1" s="2" t="s"/>
-      <c r="IE1" s="2" t="s"/>
-      <c r="IF1" s="2" t="s"/>
-      <c r="IG1" s="2" t="s"/>
+      <c r="IA1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="IB1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="ID1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="IE1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="IF1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="IG1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="IH1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="II1" s="2" t="s"/>
-      <c r="IJ1" s="2" t="s"/>
-      <c r="IL1" s="2" t="s"/>
-      <c r="IM1" s="2" t="s"/>
-      <c r="IN1" s="2" t="s"/>
-      <c r="IO1" s="2" t="s"/>
+      <c r="II1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="IJ1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="IL1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="IM1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="IN1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="IO1" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="IP1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="IQ1" s="2" t="s"/>
-      <c r="IR1" s="2" t="s"/>
+      <c r="IQ1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="IR1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="2:252">
       <c r="B2" t="s">
@@ -4158,7 +4530,9 @@
       <c r="BN2" s="2"/>
       <c r="BO2" s="2"/>
       <c r="BP2" s="2"/>
-      <c r="HN2" t="s"/>
+      <c r="HN2" t="s">
+        <v>10</v>
+      </c>
       <c r="HU2" t="s">
         <v>11</v>
       </c>
@@ -4198,26 +4572,42 @@
         <f>+AK3+1</f>
         <v>46179</v>
       </c>
-      <c r="AT3"/>
-      <c r="AU3"/>
-      <c r="AY3"/>
+      <c r="AT3">
+        <v>2</v>
+      </c>
+      <c r="AU3">
+        <v>2</v>
+      </c>
+      <c r="AY3">
+        <v>1</v>
+      </c>
       <c r="BA3" s="3">
         <f>+AS3+1</f>
         <v>46180</v>
       </c>
-      <c r="BB3"/>
-      <c r="BC3"/>
+      <c r="BB3">
+        <v>1</v>
+      </c>
+      <c r="BC3">
+        <v>3</v>
+      </c>
       <c r="BD3" s="2"/>
       <c r="BE3" s="26"/>
       <c r="BF3" s="2"/>
-      <c r="BG3" s="2"/>
+      <c r="BG3" s="2">
+        <v>1</v>
+      </c>
       <c r="BH3" s="2"/>
       <c r="BI3" s="3">
         <f>+BA3+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ3"/>
-      <c r="BK3"/>
+      <c r="BJ3">
+        <v>1</v>
+      </c>
+      <c r="BK3">
+        <v>4</v>
+      </c>
       <c r="BL3" s="23"/>
       <c r="BM3" s="23"/>
       <c r="BN3" s="23"/>
@@ -4227,16 +4617,28 @@
         <f>+BI3+1</f>
         <v>46182</v>
       </c>
-      <c r="BR3"/>
-      <c r="BS3"/>
+      <c r="BR3">
+        <v>1</v>
+      </c>
+      <c r="BS3">
+        <v>4</v>
+      </c>
       <c r="BY3" s="3">
         <f>+BQ3+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ3"/>
-      <c r="CA3"/>
-      <c r="CC3"/>
-      <c r="CE3"/>
+      <c r="BZ3">
+        <v>1</v>
+      </c>
+      <c r="CA3">
+        <v>3</v>
+      </c>
+      <c r="CC3">
+        <v>1</v>
+      </c>
+      <c r="CE3">
+        <v>1</v>
+      </c>
       <c r="CG3" s="3">
         <f>+BY3+1</f>
         <v>46184</v>
@@ -4352,37 +4754,67 @@
         <f>+AK4+1</f>
         <v>46179</v>
       </c>
-      <c r="AT4"/>
-      <c r="AU4"/>
-      <c r="AY4"/>
+      <c r="AT4">
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <v>4</v>
+      </c>
+      <c r="AY4">
+        <v>1</v>
+      </c>
       <c r="BA4" s="3">
         <f>+AS4+1</f>
         <v>46180</v>
       </c>
-      <c r="BB4"/>
-      <c r="BC4"/>
-      <c r="BG4"/>
+      <c r="BB4">
+        <v>1</v>
+      </c>
+      <c r="BC4">
+        <v>3</v>
+      </c>
+      <c r="BG4">
+        <v>1</v>
+      </c>
       <c r="BI4" s="3">
         <f>+BA4+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ4"/>
-      <c r="BK4"/>
-      <c r="BO4"/>
+      <c r="BJ4">
+        <v>1</v>
+      </c>
+      <c r="BK4">
+        <v>3</v>
+      </c>
+      <c r="BO4">
+        <v>1</v>
+      </c>
       <c r="BQ4" s="3">
         <f>+BI4+1</f>
         <v>46182</v>
       </c>
-      <c r="BR4"/>
-      <c r="BS4"/>
-      <c r="BW4"/>
+      <c r="BR4">
+        <v>1</v>
+      </c>
+      <c r="BS4">
+        <v>3</v>
+      </c>
+      <c r="BW4">
+        <v>1</v>
+      </c>
       <c r="BY4" s="3">
         <f>+BQ4+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ4"/>
-      <c r="CA4"/>
-      <c r="CE4"/>
+      <c r="BZ4">
+        <v>1</v>
+      </c>
+      <c r="CA4">
+        <v>3</v>
+      </c>
+      <c r="CE4">
+        <v>1</v>
+      </c>
       <c r="CG4" s="3">
         <f>+BY4+1</f>
         <v>46184</v>
@@ -4497,29 +4929,43 @@
         <f>+AK5+1</f>
         <v>46179</v>
       </c>
-      <c r="AT5"/>
-      <c r="AY5"/>
-      <c r="AZ5"/>
+      <c r="AT5">
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
       <c r="BA5" s="3">
         <f>+AS5+1</f>
         <v>46180</v>
       </c>
-      <c r="BB5"/>
+      <c r="BB5">
+        <v>1</v>
+      </c>
       <c r="BI5" s="3">
         <f>+BA5+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ5"/>
+      <c r="BJ5">
+        <v>1</v>
+      </c>
       <c r="BQ5" s="3">
         <f>+BI5+1</f>
         <v>46182</v>
       </c>
-      <c r="BR5"/>
+      <c r="BR5">
+        <v>1</v>
+      </c>
       <c r="BY5" s="3">
         <f>+BQ5+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ5"/>
+      <c r="BZ5">
+        <v>1</v>
+      </c>
       <c r="CG5" s="3">
         <f>+BY5+1</f>
         <v>46184</v>
@@ -4764,27 +5210,37 @@
         <f>+AK7+1</f>
         <v>46179</v>
       </c>
-      <c r="AT7"/>
+      <c r="AT7">
+        <v>1</v>
+      </c>
       <c r="BA7" s="3">
         <f>+AS7+1</f>
         <v>46180</v>
       </c>
-      <c r="BB7"/>
+      <c r="BB7">
+        <v>1</v>
+      </c>
       <c r="BI7" s="3">
         <f>+BA7+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ7"/>
+      <c r="BJ7">
+        <v>1</v>
+      </c>
       <c r="BQ7" s="3">
         <f>+BI7+1</f>
         <v>46182</v>
       </c>
-      <c r="BR7"/>
+      <c r="BR7">
+        <v>1</v>
+      </c>
       <c r="BY7" s="3">
         <f>+BQ7+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ7"/>
+      <c r="BZ7">
+        <v>1</v>
+      </c>
       <c r="CG7" s="3">
         <f>+BY7+1</f>
         <v>46184</v>
@@ -4911,12 +5367,16 @@
         <f>+BI8+1</f>
         <v>46182</v>
       </c>
-      <c r="BR8"/>
+      <c r="BR8">
+        <v>1</v>
+      </c>
       <c r="BY8" s="3">
         <f>+BQ8+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ8"/>
+      <c r="BZ8">
+        <v>1</v>
+      </c>
       <c r="CG8" s="3">
         <f>+BY8+1</f>
         <v>46184</v>
@@ -5291,38 +5751,70 @@
         <f>+AK11+1</f>
         <v>46179</v>
       </c>
-      <c r="AT11"/>
-      <c r="AU11"/>
-      <c r="AW11"/>
-      <c r="AY11"/>
+      <c r="AT11">
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>2</v>
+      </c>
+      <c r="AW11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
       <c r="BA11" s="3">
         <f>+AS11+1</f>
         <v>46180</v>
       </c>
-      <c r="BB11"/>
-      <c r="BC11"/>
-      <c r="BE11"/>
-      <c r="BG11"/>
+      <c r="BB11">
+        <v>1</v>
+      </c>
+      <c r="BC11">
+        <v>3</v>
+      </c>
+      <c r="BE11">
+        <v>1</v>
+      </c>
+      <c r="BG11">
+        <v>1</v>
+      </c>
       <c r="BI11" s="3">
         <f>+BA11+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ11"/>
-      <c r="BK11"/>
-      <c r="BO11"/>
+      <c r="BJ11">
+        <v>1</v>
+      </c>
+      <c r="BK11">
+        <v>3</v>
+      </c>
+      <c r="BO11">
+        <v>1</v>
+      </c>
       <c r="BQ11" s="3">
         <f>+BI11+1</f>
         <v>46182</v>
       </c>
-      <c r="BR11"/>
-      <c r="BS11"/>
-      <c r="BU11"/>
+      <c r="BR11">
+        <v>1</v>
+      </c>
+      <c r="BS11">
+        <v>3</v>
+      </c>
+      <c r="BU11">
+        <v>1</v>
+      </c>
       <c r="BY11" s="3">
         <f>+BQ11+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ11"/>
-      <c r="CA11"/>
+      <c r="BZ11">
+        <v>1</v>
+      </c>
+      <c r="CA11">
+        <v>3</v>
+      </c>
       <c r="CG11" s="3">
         <f>+BY11+1</f>
         <v>46184</v>
@@ -5441,7 +5933,9 @@
         <f>+AS12+1</f>
         <v>46180</v>
       </c>
-      <c r="BB12"/>
+      <c r="BB12">
+        <v>1</v>
+      </c>
       <c r="BI12" s="3">
         <f>+BA12+1</f>
         <v>46181</v>
@@ -5698,35 +6192,61 @@
         <f>+AK14+1</f>
         <v>46179</v>
       </c>
-      <c r="AU14"/>
+      <c r="AU14">
+        <v>1</v>
+      </c>
       <c r="BA14" s="3">
         <f>+AS14+1</f>
         <v>46180</v>
       </c>
-      <c r="BB14"/>
-      <c r="BC14"/>
-      <c r="BG14"/>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>3</v>
+      </c>
+      <c r="BG14">
+        <v>1</v>
+      </c>
       <c r="BI14" s="3">
         <f>+BA14+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ14"/>
-      <c r="BK14"/>
-      <c r="BO14"/>
+      <c r="BJ14">
+        <v>1</v>
+      </c>
+      <c r="BK14">
+        <v>3</v>
+      </c>
+      <c r="BO14">
+        <v>1</v>
+      </c>
       <c r="BQ14" s="3">
         <f>+BI14+1</f>
         <v>46182</v>
       </c>
-      <c r="BR14"/>
-      <c r="BS14"/>
-      <c r="BW14"/>
+      <c r="BR14">
+        <v>1</v>
+      </c>
+      <c r="BS14">
+        <v>3</v>
+      </c>
+      <c r="BW14">
+        <v>1</v>
+      </c>
       <c r="BY14" s="3">
         <f>+BQ14+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ14"/>
-      <c r="CA14"/>
-      <c r="CE14"/>
+      <c r="BZ14">
+        <v>1</v>
+      </c>
+      <c r="CA14">
+        <v>3</v>
+      </c>
+      <c r="CE14">
+        <v>1</v>
+      </c>
       <c r="CG14" s="3">
         <f>+BY14+1</f>
         <v>46184</v>
@@ -5971,19 +6491,29 @@
         <f>+AK16+1</f>
         <v>46179</v>
       </c>
-      <c r="AT16"/>
-      <c r="AU16"/>
+      <c r="AT16">
+        <v>1</v>
+      </c>
+      <c r="AU16">
+        <v>2</v>
+      </c>
       <c r="BA16" s="3">
         <f>+AS16+1</f>
         <v>46180</v>
       </c>
-      <c r="BB16"/>
-      <c r="BC16"/>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>3</v>
+      </c>
       <c r="BI16" s="3">
         <f>+BA16+1</f>
         <v>46181</v>
       </c>
-      <c r="BK16"/>
+      <c r="BK16">
+        <v>2</v>
+      </c>
       <c r="BQ16" s="3">
         <f>+BI16+1</f>
         <v>46182</v>
@@ -5992,8 +6522,12 @@
         <f>+BQ16+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ16"/>
-      <c r="CA16"/>
+      <c r="BZ16">
+        <v>1</v>
+      </c>
+      <c r="CA16">
+        <v>3</v>
+      </c>
       <c r="CG16" s="3">
         <f>+BY16+1</f>
         <v>46184</v>
@@ -6238,23 +6772,31 @@
         <f>+AK18+1</f>
         <v>46179</v>
       </c>
-      <c r="AT18"/>
+      <c r="AT18">
+        <v>1</v>
+      </c>
       <c r="BA18" s="3">
         <f>+AS18+1</f>
         <v>46180</v>
       </c>
-      <c r="BB18"/>
+      <c r="BB18">
+        <v>1</v>
+      </c>
       <c r="BD18" s="4"/>
       <c r="BI18" s="3">
         <f>+BA18+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ18"/>
+      <c r="BJ18">
+        <v>1</v>
+      </c>
       <c r="BQ18" s="3">
         <f>+BI18+1</f>
         <v>46182</v>
       </c>
-      <c r="BR18"/>
+      <c r="BR18">
+        <v>1</v>
+      </c>
       <c r="BY18" s="3">
         <f>+BQ18+1</f>
         <v>46183</v>
@@ -6507,17 +7049,23 @@
         <f>+AS20+1</f>
         <v>46180</v>
       </c>
-      <c r="BB20"/>
+      <c r="BB20">
+        <v>1</v>
+      </c>
       <c r="BI20" s="3">
         <f>+BA20+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ20"/>
+      <c r="BJ20">
+        <v>1</v>
+      </c>
       <c r="BQ20" s="3">
         <f>+BI20+1</f>
         <v>46182</v>
       </c>
-      <c r="BR20"/>
+      <c r="BR20">
+        <v>1</v>
+      </c>
       <c r="BY20" s="3">
         <f>+BQ20+1</f>
         <v>46183</v>
@@ -6904,12 +7452,16 @@
         <f>+BA23+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ23"/>
+      <c r="BJ23">
+        <v>1</v>
+      </c>
       <c r="BQ23" s="3">
         <f>+BI23+1</f>
         <v>46182</v>
       </c>
-      <c r="BR23"/>
+      <c r="BR23">
+        <v>1</v>
+      </c>
       <c r="BY23" s="3">
         <f>+BQ23+1</f>
         <v>46183</v>
@@ -7158,19 +7710,29 @@
         <f>+AK25+1</f>
         <v>46179</v>
       </c>
-      <c r="AT25"/>
-      <c r="AY25"/>
-      <c r="AZ25"/>
+      <c r="AT25">
+        <v>1</v>
+      </c>
+      <c r="AY25">
+        <v>1</v>
+      </c>
+      <c r="AZ25">
+        <v>1</v>
+      </c>
       <c r="BA25" s="3">
         <f>+AS25+1</f>
         <v>46180</v>
       </c>
-      <c r="BB25"/>
+      <c r="BB25">
+        <v>1</v>
+      </c>
       <c r="BI25" s="3">
         <f>+BA25+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ25"/>
+      <c r="BJ25">
+        <v>1</v>
+      </c>
       <c r="BQ25" s="3">
         <f>+BI25+1</f>
         <v>46182</v>
@@ -7179,7 +7741,9 @@
         <f>+BQ25+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ25"/>
+      <c r="BZ25">
+        <v>1</v>
+      </c>
       <c r="CG25" s="3">
         <f>+BY25+1</f>
         <v>46184</v>
@@ -7294,17 +7858,23 @@
         <f>+AK26+1</f>
         <v>46179</v>
       </c>
-      <c r="AT26"/>
+      <c r="AT26">
+        <v>1</v>
+      </c>
       <c r="BA26" s="3">
         <f>+AS26+1</f>
         <v>46180</v>
       </c>
-      <c r="BB26"/>
+      <c r="BB26">
+        <v>1</v>
+      </c>
       <c r="BI26" s="3">
         <f>+BA26+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ26"/>
+      <c r="BJ26">
+        <v>1</v>
+      </c>
       <c r="BQ26" s="3">
         <f>+BI26+1</f>
         <v>46182</v>
@@ -7313,7 +7883,9 @@
         <f>+BQ26+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ26"/>
+      <c r="BZ26">
+        <v>1</v>
+      </c>
       <c r="CG26" s="25">
         <f>+BY26+1</f>
         <v>46184</v>
@@ -7428,27 +8000,37 @@
         <f>+AK27+1</f>
         <v>46179</v>
       </c>
-      <c r="AT27"/>
+      <c r="AT27">
+        <v>1</v>
+      </c>
       <c r="BA27" s="3">
         <f>+AS27+1</f>
         <v>46180</v>
       </c>
-      <c r="BB27"/>
+      <c r="BB27">
+        <v>1</v>
+      </c>
       <c r="BI27" s="3">
         <f>+BA27+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ27"/>
+      <c r="BJ27">
+        <v>1</v>
+      </c>
       <c r="BQ27" s="3">
         <f>+BI27+1</f>
         <v>46182</v>
       </c>
-      <c r="BR27"/>
+      <c r="BR27">
+        <v>1</v>
+      </c>
       <c r="BY27" s="3">
         <f>+BQ27+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ27"/>
+      <c r="BZ27">
+        <v>1</v>
+      </c>
       <c r="CG27" s="3">
         <f>+BY27+1</f>
         <v>46184</v>
@@ -7567,17 +8149,23 @@
         <f>+AS28+1</f>
         <v>46180</v>
       </c>
-      <c r="BB28"/>
+      <c r="BB28">
+        <v>1</v>
+      </c>
       <c r="BI28" s="3">
         <f>+BA28+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ28"/>
+      <c r="BJ28">
+        <v>2</v>
+      </c>
       <c r="BQ28" s="3">
         <f>+BI28+1</f>
         <v>46182</v>
       </c>
-      <c r="BR28"/>
+      <c r="BR28">
+        <v>1</v>
+      </c>
       <c r="BY28" s="3">
         <f>+BQ28+1</f>
         <v>46183</v>
@@ -7696,7 +8284,9 @@
         <f>+AK29+1</f>
         <v>46179</v>
       </c>
-      <c r="AT29"/>
+      <c r="AT29">
+        <v>1</v>
+      </c>
       <c r="BA29" s="3">
         <f>+AS29+1</f>
         <v>46180</v>
@@ -7827,7 +8417,9 @@
         <f>+AK30+1</f>
         <v>46179</v>
       </c>
-      <c r="AT30"/>
+      <c r="AT30">
+        <v>1</v>
+      </c>
       <c r="BA30" s="3">
         <f>+AS30+1</f>
         <v>46180</v>
@@ -7836,7 +8428,9 @@
         <f>+BA30+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ30"/>
+      <c r="BJ30">
+        <v>1</v>
+      </c>
       <c r="BQ30" s="3">
         <f>+BI30+1</f>
         <v>46182</v>
@@ -8089,7 +8683,9 @@
         <f>+AK32+1</f>
         <v>46179</v>
       </c>
-      <c r="AT32"/>
+      <c r="AT32">
+        <v>1</v>
+      </c>
       <c r="BA32" s="3">
         <f>+AS32+1</f>
         <v>46180</v>
@@ -8098,12 +8694,16 @@
         <f>+BA32+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ32"/>
+      <c r="BJ32">
+        <v>1</v>
+      </c>
       <c r="BQ32" s="3">
         <f>+BI32+1</f>
         <v>46182</v>
       </c>
-      <c r="BR32"/>
+      <c r="BR32">
+        <v>1</v>
+      </c>
       <c r="BY32" s="3">
         <f>+BQ32+1</f>
         <v>46183</v>
@@ -8221,9 +8821,15 @@
         <f>+AK33+1</f>
         <v>46179</v>
       </c>
-      <c r="AT33"/>
-      <c r="AY33"/>
-      <c r="AZ33"/>
+      <c r="AT33">
+        <v>1</v>
+      </c>
+      <c r="AY33">
+        <v>1</v>
+      </c>
+      <c r="AZ33">
+        <v>1</v>
+      </c>
       <c r="BA33" s="3">
         <f>+AS33+1</f>
         <v>46180</v>
@@ -8232,7 +8838,9 @@
         <f>+BA33+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ33"/>
+      <c r="BJ33">
+        <v>1</v>
+      </c>
       <c r="BQ33" s="3">
         <f>+BI33+1</f>
         <v>46182</v>
@@ -8354,34 +8962,58 @@
         <f>+AK34+1</f>
         <v>46179</v>
       </c>
-      <c r="AU34"/>
+      <c r="AU34">
+        <v>1</v>
+      </c>
       <c r="BA34" s="3">
         <f>+AS34+1</f>
         <v>46180</v>
       </c>
-      <c r="BB34"/>
-      <c r="BC34"/>
+      <c r="BB34">
+        <v>1</v>
+      </c>
+      <c r="BC34">
+        <v>3</v>
+      </c>
       <c r="BI34" s="3">
         <f>+BA34+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ34"/>
-      <c r="BK34"/>
-      <c r="BO34"/>
+      <c r="BJ34">
+        <v>1</v>
+      </c>
+      <c r="BK34">
+        <v>3</v>
+      </c>
+      <c r="BO34">
+        <v>1</v>
+      </c>
       <c r="BQ34" s="3">
         <f>+BI34+1</f>
         <v>46182</v>
       </c>
-      <c r="BR34"/>
-      <c r="BS34"/>
-      <c r="BW34"/>
+      <c r="BR34">
+        <v>1</v>
+      </c>
+      <c r="BS34">
+        <v>3</v>
+      </c>
+      <c r="BW34">
+        <v>1</v>
+      </c>
       <c r="BY34" s="3">
         <f>+BQ34+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ34"/>
-      <c r="CA34"/>
-      <c r="CE34"/>
+      <c r="BZ34">
+        <v>1</v>
+      </c>
+      <c r="CA34">
+        <v>3</v>
+      </c>
+      <c r="CE34">
+        <v>1</v>
+      </c>
       <c r="CG34" s="3">
         <f>+BY34+1</f>
         <v>46184</v>
@@ -8753,7 +9385,9 @@
         <f>+AK37+1</f>
         <v>46179</v>
       </c>
-      <c r="AT37"/>
+      <c r="AT37">
+        <v>1</v>
+      </c>
       <c r="BA37" s="3">
         <f>+AS37+1</f>
         <v>46180</v>
@@ -8766,7 +9400,9 @@
         <f>+BI37+1</f>
         <v>46182</v>
       </c>
-      <c r="BR37"/>
+      <c r="BR37">
+        <v>1</v>
+      </c>
       <c r="BY37" s="3">
         <f>+BQ37+1</f>
         <v>46183</v>
@@ -8888,7 +9524,9 @@
         <f>+AS38+1</f>
         <v>46180</v>
       </c>
-      <c r="BB38"/>
+      <c r="BB38">
+        <v>1</v>
+      </c>
       <c r="BI38" s="3">
         <f>+BA38+1</f>
         <v>46181</v>
@@ -8897,7 +9535,9 @@
         <f>+BI38+1</f>
         <v>46182</v>
       </c>
-      <c r="BR38"/>
+      <c r="BR38">
+        <v>1</v>
+      </c>
       <c r="BY38" s="3">
         <f>+BQ38+1</f>
         <v>46183</v>
@@ -9015,7 +9655,9 @@
         <f>+AK39+1</f>
         <v>46179</v>
       </c>
-      <c r="AT39"/>
+      <c r="AT39">
+        <v>1</v>
+      </c>
       <c r="BA39" s="3">
         <f>+AS39+1</f>
         <v>46180</v>
@@ -9024,12 +9666,16 @@
         <f>+BA39+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ39"/>
+      <c r="BJ39">
+        <v>1</v>
+      </c>
       <c r="BQ39" s="3">
         <f>+BI39+1</f>
         <v>46182</v>
       </c>
-      <c r="BR39"/>
+      <c r="BR39">
+        <v>1</v>
+      </c>
       <c r="BY39" s="3">
         <f>+BQ39+1</f>
         <v>46183</v>
@@ -9151,22 +9797,30 @@
         <f>+AS40+1</f>
         <v>46180</v>
       </c>
-      <c r="BB40"/>
+      <c r="BB40">
+        <v>2</v>
+      </c>
       <c r="BI40" s="3">
         <f>+BA40+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ40"/>
+      <c r="BJ40">
+        <v>1</v>
+      </c>
       <c r="BQ40" s="3">
         <f>+BI40+1</f>
         <v>46182</v>
       </c>
-      <c r="BR40"/>
+      <c r="BR40">
+        <v>1</v>
+      </c>
       <c r="BY40" s="3">
         <f>+BQ40+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ40"/>
+      <c r="BZ40">
+        <v>1</v>
+      </c>
       <c r="CG40" s="3">
         <f>+BY40+1</f>
         <v>46184</v>
@@ -9280,33 +9934,55 @@
         <f>+AK41+1</f>
         <v>46179</v>
       </c>
-      <c r="AU41"/>
+      <c r="AU41">
+        <v>1</v>
+      </c>
       <c r="BA41" s="3">
         <f>+AS41+1</f>
         <v>46180</v>
       </c>
-      <c r="BB41"/>
-      <c r="BC41"/>
-      <c r="BG41"/>
+      <c r="BB41">
+        <v>1</v>
+      </c>
+      <c r="BC41">
+        <v>2</v>
+      </c>
+      <c r="BG41">
+        <v>1</v>
+      </c>
       <c r="BI41" s="3">
         <f>+BA41+1</f>
         <v>46181</v>
       </c>
-      <c r="BK41"/>
+      <c r="BK41">
+        <v>1</v>
+      </c>
       <c r="BQ41" s="3">
         <f>+BI41+1</f>
         <v>46182</v>
       </c>
-      <c r="BR41"/>
-      <c r="BS41"/>
-      <c r="BW41"/>
+      <c r="BR41">
+        <v>1</v>
+      </c>
+      <c r="BS41">
+        <v>3</v>
+      </c>
+      <c r="BW41">
+        <v>1</v>
+      </c>
       <c r="BY41" s="3">
         <f>+BQ41+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ41"/>
-      <c r="CA41"/>
-      <c r="CE41"/>
+      <c r="BZ41">
+        <v>1</v>
+      </c>
+      <c r="CA41">
+        <v>3</v>
+      </c>
+      <c r="CE41">
+        <v>1</v>
+      </c>
       <c r="CG41" s="3">
         <f>+BY41+1</f>
         <v>46184</v>
@@ -9549,18 +10225,26 @@
         <f>+AK43+1</f>
         <v>46179</v>
       </c>
-      <c r="AU43"/>
+      <c r="AU43">
+        <v>1</v>
+      </c>
       <c r="BA43" s="3">
         <f>+AS43+1</f>
         <v>46180</v>
       </c>
-      <c r="BB43"/>
-      <c r="BC43"/>
+      <c r="BB43">
+        <v>1</v>
+      </c>
+      <c r="BC43">
+        <v>2</v>
+      </c>
       <c r="BI43" s="3">
         <f>+BA43+1</f>
         <v>46181</v>
       </c>
-      <c r="BK43"/>
+      <c r="BK43">
+        <v>1</v>
+      </c>
       <c r="BQ43" s="3">
         <f>+BI43+1</f>
         <v>46182</v>
@@ -9569,7 +10253,9 @@
         <f>+BQ43+1</f>
         <v>46183</v>
       </c>
-      <c r="CA43"/>
+      <c r="CA43">
+        <v>1</v>
+      </c>
       <c r="CG43" s="3">
         <f>+BY43+1</f>
         <v>46184</v>
@@ -9688,20 +10374,32 @@
         <f>+BA44+1</f>
         <v>46181</v>
       </c>
-      <c r="BK44"/>
+      <c r="BK44">
+        <v>1</v>
+      </c>
       <c r="BQ44" s="3">
         <f>+BI44+1</f>
         <v>46182</v>
       </c>
-      <c r="BR44"/>
-      <c r="BS44"/>
-      <c r="BW44"/>
+      <c r="BR44">
+        <v>1</v>
+      </c>
+      <c r="BS44">
+        <v>4</v>
+      </c>
+      <c r="BW44">
+        <v>1</v>
+      </c>
       <c r="BY44" s="3">
         <f>+BQ44+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ44"/>
-      <c r="CA44"/>
+      <c r="BZ44">
+        <v>1</v>
+      </c>
+      <c r="CA44">
+        <v>6</v>
+      </c>
       <c r="CG44" s="3">
         <f>+BY44+1</f>
         <v>46184</v>
@@ -9941,27 +10639,37 @@
         <f>+AK46+1</f>
         <v>46179</v>
       </c>
-      <c r="AT46"/>
+      <c r="AT46">
+        <v>1</v>
+      </c>
       <c r="BA46" s="3">
         <f>+AS46+1</f>
         <v>46180</v>
       </c>
-      <c r="BB46"/>
+      <c r="BB46">
+        <v>1</v>
+      </c>
       <c r="BI46" s="3">
         <f>+BA46+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ46"/>
+      <c r="BJ46">
+        <v>1</v>
+      </c>
       <c r="BQ46" s="3">
         <f>+BI46+1</f>
         <v>46182</v>
       </c>
-      <c r="BR46"/>
+      <c r="BR46">
+        <v>1</v>
+      </c>
       <c r="BY46" s="3">
         <f>+BQ46+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ46"/>
+      <c r="BZ46">
+        <v>1</v>
+      </c>
       <c r="CG46" s="3">
         <f>+BY46+1</f>
         <v>46184</v>
@@ -10075,27 +10783,37 @@
         <f>+AK47+1</f>
         <v>46179</v>
       </c>
-      <c r="AT47"/>
+      <c r="AT47">
+        <v>1</v>
+      </c>
       <c r="BA47" s="3">
         <f>+AS47+1</f>
         <v>46180</v>
       </c>
-      <c r="BB47"/>
+      <c r="BB47">
+        <v>1</v>
+      </c>
       <c r="BI47" s="3">
         <f>+BA47+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ47"/>
+      <c r="BJ47">
+        <v>1</v>
+      </c>
       <c r="BQ47" s="3">
         <f>+BI47+1</f>
         <v>46182</v>
       </c>
-      <c r="BR47"/>
+      <c r="BR47">
+        <v>1</v>
+      </c>
       <c r="BY47" s="3">
         <f>+BQ47+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ47"/>
+      <c r="BZ47">
+        <v>1</v>
+      </c>
       <c r="CG47" s="3">
         <f>+BY47+1</f>
         <v>46184</v>
@@ -10209,36 +10927,64 @@
         <f>+AK48+1</f>
         <v>46179</v>
       </c>
-      <c r="AT48"/>
-      <c r="AU48"/>
-      <c r="AY48"/>
-      <c r="AZ48"/>
+      <c r="AT48">
+        <v>1</v>
+      </c>
+      <c r="AU48">
+        <v>1</v>
+      </c>
+      <c r="AY48">
+        <v>1</v>
+      </c>
+      <c r="AZ48">
+        <v>1</v>
+      </c>
       <c r="BA48" s="3">
         <f>+AS48+1</f>
         <v>46180</v>
       </c>
-      <c r="BB48"/>
-      <c r="BC48"/>
+      <c r="BB48">
+        <v>1</v>
+      </c>
+      <c r="BC48">
+        <v>2</v>
+      </c>
       <c r="BI48" s="3">
         <f>+BA48+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ48"/>
-      <c r="BK48"/>
+      <c r="BJ48">
+        <v>1</v>
+      </c>
+      <c r="BK48">
+        <v>2</v>
+      </c>
       <c r="BQ48" s="3">
         <f>+BI48+1</f>
         <v>46182</v>
       </c>
-      <c r="BR48"/>
-      <c r="BS48"/>
+      <c r="BR48">
+        <v>1</v>
+      </c>
+      <c r="BS48">
+        <v>1</v>
+      </c>
       <c r="BY48" s="3">
         <f>+BQ48+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ48"/>
-      <c r="CA48"/>
-      <c r="CE48"/>
-      <c r="CF48"/>
+      <c r="BZ48">
+        <v>1</v>
+      </c>
+      <c r="CA48">
+        <v>3</v>
+      </c>
+      <c r="CE48">
+        <v>1</v>
+      </c>
+      <c r="CF48">
+        <v>1</v>
+      </c>
       <c r="CG48" s="3">
         <f>+BY48+1</f>
         <v>46184</v>
@@ -10610,34 +11356,58 @@
         <f>+AK51+1</f>
         <v>46179</v>
       </c>
-      <c r="AU51"/>
+      <c r="AU51">
+        <v>1</v>
+      </c>
       <c r="BA51" s="3">
         <f>+AS51+1</f>
         <v>46180</v>
       </c>
-      <c r="BB51"/>
-      <c r="BC51"/>
-      <c r="BG51"/>
+      <c r="BB51">
+        <v>1</v>
+      </c>
+      <c r="BC51">
+        <v>3</v>
+      </c>
+      <c r="BG51">
+        <v>1</v>
+      </c>
       <c r="BI51" s="3">
         <f>+BA51+1</f>
         <v>46181</v>
       </c>
-      <c r="BJ51"/>
-      <c r="BK51"/>
+      <c r="BJ51">
+        <v>1</v>
+      </c>
+      <c r="BK51">
+        <v>3</v>
+      </c>
       <c r="BQ51" s="3">
         <f>+BI51+1</f>
         <v>46182</v>
       </c>
-      <c r="BR51"/>
-      <c r="BS51"/>
-      <c r="BW51"/>
+      <c r="BR51">
+        <v>2</v>
+      </c>
+      <c r="BS51">
+        <v>5</v>
+      </c>
+      <c r="BW51">
+        <v>1</v>
+      </c>
       <c r="BY51" s="3">
         <f>+BQ51+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ51"/>
-      <c r="CA51"/>
-      <c r="CE51"/>
+      <c r="BZ51">
+        <v>1</v>
+      </c>
+      <c r="CA51">
+        <v>3</v>
+      </c>
+      <c r="CE51">
+        <v>1</v>
+      </c>
       <c r="CG51" s="3">
         <f>+BY51+1</f>
         <v>46184</v>
@@ -10877,31 +11647,49 @@
         <f>+AK53+1</f>
         <v>46179</v>
       </c>
-      <c r="AT53"/>
-      <c r="AU53"/>
-      <c r="AY53"/>
+      <c r="AT53">
+        <v>1</v>
+      </c>
+      <c r="AU53">
+        <v>2</v>
+      </c>
+      <c r="AY53">
+        <v>1</v>
+      </c>
       <c r="BA53" s="3">
         <f>+AS53+1</f>
         <v>46180</v>
       </c>
-      <c r="BB53"/>
-      <c r="BC53"/>
+      <c r="BB53">
+        <v>1</v>
+      </c>
+      <c r="BC53">
+        <v>3</v>
+      </c>
       <c r="BI53" s="3">
         <f>+BA53+1</f>
         <v>46181</v>
       </c>
-      <c r="BK53"/>
+      <c r="BK53">
+        <v>2</v>
+      </c>
       <c r="BQ53" s="3">
         <f>+BI53+1</f>
         <v>46182</v>
       </c>
-      <c r="BS53"/>
+      <c r="BS53">
+        <v>2</v>
+      </c>
       <c r="BY53" s="3">
         <f>+BQ53+1</f>
         <v>46183</v>
       </c>
-      <c r="BZ53"/>
-      <c r="CA53"/>
+      <c r="BZ53">
+        <v>1</v>
+      </c>
+      <c r="CA53">
+        <v>3</v>
+      </c>
       <c r="CG53" s="3">
         <f>+BY53+1</f>
         <v>46184</v>
@@ -11834,8 +12622,12 @@
         <f>F1</f>
         <v>SUPER</v>
       </c>
-      <c r="G58" t="s"/>
-      <c r="H58" t="s"/>
+      <c r="G58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>2</v>
+      </c>
       <c r="I58" t="str">
         <f>I1</f>
         <v>DRENAR</v>
@@ -11855,7 +12647,9 @@
       <c r="M58" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N58" t="s"/>
+      <c r="N58" t="s">
+        <v>67</v>
+      </c>
       <c r="V58" t="str">
         <f>V1</f>
         <v>SUPER</v>
